--- a/manuscript_submission_snapshot/additional_files/additional_file_4_secondary_endpoints_and_prediction_guardrails.xlsx
+++ b/manuscript_submission_snapshot/additional_files/additional_file_4_secondary_endpoints_and_prediction_guardrails.xlsx
@@ -7,16 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mortality_guardrail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mortality_formal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hospitalization_models" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hospitalization_status" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calibration" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decision_curve" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prediction_guardrails" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heterogeneity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endpoint_feasibility" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sheet_index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mortality_guardrail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mortality_formal" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hospitalization_models" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hospitalization_status" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="calibration" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="decision_curve" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="prediction_guardrails" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="heterogeneity" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endpoint_feasibility" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,12 +39,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,260 +433,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Workbook</t>
+          <t>README</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>additional_file_4_secondary_endpoints_and_prediction_guardrails.xlsx</t>
+          <t>Workbook overview.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Source note</t>
+          <t>mortality_guardrail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Generated from aggregate project outputs produced from approved downloaded cohort files cleaned by the authors.</t>
+          <t>Secondary mortality guardrail table.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Updated by</t>
+          <t>mortality_formal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>scripts/apply_phase48_claude_minor_fixes.py</t>
+          <t>Formal secondary Cox model outputs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Updated on</t>
+          <t>hospitalization_models</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07T11:33:36.615714+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>Header-available hospitalization candidate models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hospitalization_status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hospitalization endpoint status by cohort.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Sheet name</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Present</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>calibration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Apparent in-sample calibration diagnostics.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>README</t>
+          <t>decision_curve</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Workbook index and provenance notes.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Apparent decision-curve summaries.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mortality_guardrail</t>
+          <t>prediction_guardrails</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Earlier mortality follow-up availability and guardrail table.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Prediction interpretation guardrails.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mortality_formal</t>
+          <t>heterogeneity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Formal secondary all-cause mortality Cox guardrail models.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Cross-cohort mortality heterogeneity summaries.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hospitalization_models</t>
+          <t>endpoint_feasibility</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Header-only hospitalization candidate model comparison where available.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>hospitalization_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hospitalization candidate endpoint availability by cohort.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>calibration</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Apparent in-sample calibration metrics.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>decision_curve</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Apparent in-sample decision-curve summary.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>prediction_guardrails</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Secondary endpoint and prediction guardrail summary.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>heterogeneity</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mortality highest-class HR heterogeneity summary.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>endpoint_feasibility</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Phase47 hard-endpoint feasibility matrix across mortality, hospitalization, institutionalization and care-dependence.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Hard-endpoint feasibility matrix.</t>
         </is>
       </c>
     </row>
@@ -689,6 +578,261 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cohorts</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pooled_effect</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pooled_ci</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>q_df</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>q_p</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>i2_pct</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tau2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LFO functional deterioration adjusted RR, strict-core cohorts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CHARLS,ELSA,HRS,MHAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.3988800173131162</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.19 to 1.64</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15.186553350946443</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.001663970644456311</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80.24568227778269</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.020303899856655924</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Modified-Poisson adjusted RR for the highest crude-risk LFO class versus reference class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All-cause mortality highest-class HR, strict-core cohorts</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CHARLS,ELSA,HRS,MHAS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.368195274906255</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.99 to 2.82</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>14.110150791101832</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0027589888372402446</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>78.73871056082643</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.0231021273811249</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Secondary Cox HR for the highest mortality-HR profile class; PH guardrails still apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>All-cause mortality highest-class HR, all modelled cohorts</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CHARLS,ELSA,HRS,KLoSA,MHAS,SHARE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.2077114207122857</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.78 to 2.73</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.98889926856584</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7.591124938574214e-12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>91.80178678421068</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.06279525726275544</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Includes bridge and validation-downgraded cohorts; descriptive heterogeneity guardrail only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1687,6 +1831,273 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>additional_file_4_secondary_endpoints_and_prediction_guardrails.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source note</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Generated from aggregate project outputs produced from approved downloaded cohort files cleaned by the authors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Updated by</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>scripts/apply_phase48_claude_minor_fixes.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Updated on</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-07T11:33:36.615714+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Sheet name</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>README</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Workbook index and provenance notes.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mortality_guardrail</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Earlier mortality follow-up availability and guardrail table.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mortality_formal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Formal secondary all-cause mortality Cox guardrail models.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hospitalization_models</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Header-only hospitalization candidate model comparison where available.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hospitalization_status</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hospitalization candidate endpoint availability by cohort.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>calibration</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apparent in-sample calibration metrics.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>decision_curve</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Apparent in-sample decision-curve summary.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>prediction_guardrails</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Secondary endpoint and prediction guardrail summary.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>heterogeneity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mortality highest-class HR heterogeneity summary.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>endpoint_feasibility</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Phase47 hard-endpoint feasibility matrix across mortality, hospitalization, institutionalization and care-dependence.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2333,7 +2744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3079,7 +3490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3625,7 +4036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3925,7 +4336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4693,7 +5104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5551,7 +5962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5732,259 +6143,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>analysis</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cohorts</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>pooled_effect</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pooled_ci</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>q</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>q_df</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>q_p</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>i2_pct</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tau2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LFO functional deterioration adjusted RR, strict-core cohorts</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CHARLS,ELSA,HRS,MHAS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.3988800173131162</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.19 to 1.64</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>15.186553350946443</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.001663970644456311</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>80.24568227778269</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.020303899856655924</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Modified-Poisson adjusted RR for the highest crude-risk LFO class versus reference class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>All-cause mortality highest-class HR, strict-core cohorts</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CHARLS,ELSA,HRS,MHAS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.368195274906255</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.99 to 2.82</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>14.110150791101832</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0027589888372402446</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>78.73871056082643</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0231021273811249</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Secondary Cox HR for the highest mortality-HR profile class; PH guardrails still apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>All-cause mortality highest-class HR, all modelled cohorts</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CHARLS,ELSA,HRS,KLoSA,MHAS,SHARE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.2077114207122857</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.78 to 2.73</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.98889926856584</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>7.591124938574214e-12</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>91.80178678421068</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.06279525726275544</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Includes bridge and validation-downgraded cohorts; descriptive heterogeneity guardrail only.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>